--- a/investor_forms/007_investment_portfolio_opening_application_form--investor_forms.xlsx
+++ b/investor_forms/007_investment_portfolio_opening_application_form--investor_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1037,8 +1037,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1066,12 +1066,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'california'}</t>
+          <t>california</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'California'}</t>
+          <t>California</t>
         </is>
       </c>
     </row>
@@ -1083,12 +1083,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'new_york'}</t>
+          <t>new_york</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'New York'}</t>
+          <t>New York</t>
         </is>
       </c>
     </row>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'texas'}</t>
+          <t>texas</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Texas'}</t>
+          <t>Texas</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'checking'}</t>
+          <t>checking</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Checking'}</t>
+          <t>Checking</t>
         </is>
       </c>
     </row>
@@ -1134,12 +1134,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'savings'}</t>
+          <t>savings</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Savings'}</t>
+          <t>Savings</t>
         </is>
       </c>
     </row>
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'credit'}</t>
+          <t>credit</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Credit'}</t>
+          <t>Credit</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'handwritten'}</t>
+          <t>handwritten</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Handwritten'}</t>
+          <t>Handwritten</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'typed_goals'}</t>
+          <t>typed_goals</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Typed_goals'}</t>
+          <t>Typed goals</t>
         </is>
       </c>
     </row>
